--- a/models/sovereigns/Serbia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Serbia_Sovereign_Model.xlsx
@@ -820,16 +820,34 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>-2.9</v>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -923,16 +941,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>3.937</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -940,16 +976,34 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>34.151</v>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -974,16 +1028,34 @@
           <t>import_cover_months</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
+      <c r="B18" s="2" t="n">
+        <v>6.161</v>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>months</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1042,16 +1114,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>112.025</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Serbia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Serbia_Sovereign_Model.xlsx
@@ -652,12 +652,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>National Bank of Serbia</t>
+          <t>National Bank of Serbia, Executive Board decision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>10-Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Statistical Office of Serbia</t>
+          <t>Statistical Office of the Republic of Serbia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -726,12 +726,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>Q2-26 YoY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Statistical Office of Serbia</t>
+          <t>Statistical Office of the Republic of Serbia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -739,11 +739,7 @@
           <t>Sep-26</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>projection range 3.2-3.4; Q2-26 3.8% y/y</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -778,12 +774,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>end-Aug-26</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Public Debt Administration</t>
+          <t>Public Debt Administration (javnidug.gov.rs)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -793,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>general government, EUR 41.93bn</t>
+          <t>General government debt, EUR 41.93bn</t>
         </is>
       </c>
     </row>
@@ -929,11 +925,7 @@
           <t>Jun-26</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>net FDI EUR 3.8-4.2bn covers it</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -977,7 +969,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>34.151</v>
+        <v>35.71</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -986,12 +978,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>IMF International Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1001,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Gross official reserves incl. gold at national valuation, end-month (auto-filled; a run's sourced point replaces it unless older)</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1021,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>6.161</v>
+        <v>6.2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1038,24 +1030,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>National Bank of Serbia (goods and services imports)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1307,12 +1295,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PCI (36-month, non-financing)</t>
+          <t>Policy Coordination Instrument (36-month, non-financing, through late 2027)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15-Dec-26 (4th review mission)</t>
+          <t>Fourth Review mission 15-Dec-26</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1341,10 +1329,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1357,7 +1350,8 @@
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1365,10 +1359,11 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1377,7 +1372,8 @@
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1385,10 +1381,15 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n">
         <v>-4.1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>National Bank of Serbia / IMF, Jun-26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1397,7 +1398,8 @@
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1406,7 +1408,8 @@
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1415,9 +1418,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>43.3</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Public Debt Administration, Aug-26 (end-2024 figure cited as comparison)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1426,7 +1436,8 @@
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1435,7 +1446,8 @@
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1444,7 +1456,8 @@
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1453,7 +1466,8 @@
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Serbia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Serbia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/serbia.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/serbia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Serbia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Serbia_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>National Bank of Serbia, Executive Board decision</t>
+          <t>National Bank of Serbia Executive Board</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Policy Coordination Instrument (36-month, non-financing, through late 2027)</t>
+          <t>36-month non-financing Policy Coordination Instrument (third review completed 15-Jun-26)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fourth Review mission 15-Dec-26</t>
+          <t>Fourth review mission 15-Dec-26</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Public Debt Administration, Aug-26 (end-2024 figure cited as comparison)</t>
+          <t>Public Debt Administration, Aug-26 (end-2024 figure cited as 47.7%)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Serbia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Serbia_Sovereign_Model.xlsx
@@ -647,12 +647,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>Oct-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>National Bank of Serbia Executive Board</t>
+          <t>National Bank of Serbia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -779,12 +779,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Public Debt Administration (javnidug.gov.rs)</t>
+          <t>Public Debt Administration</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-2.9</v>
+        <v>-3.25</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -826,24 +826,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2026 target (midpoint of 3.0-3.5% of GDP range)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>Ministry of Finance</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+          <t>31-Aug-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -922,7 +918,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1040,7 +1036,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>10-Sep-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1295,12 +1291,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>36-month non-financing Policy Coordination Instrument (third review completed 15-Jun-26)</t>
+          <t>Policy Coordination Instrument (36-month, non-financing)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fourth review mission 15-Dec-26</t>
+          <t>15-Dec-26 (Fourth Review mission)</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1359,11 @@
       <c r="C3" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Statistical Office of the Republic of Serbia, Sep-26 (midpoint of 3.2-3.4% projection)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1398,8 +1398,14 @@
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" s="2" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ministry of Finance, Aug-26 (midpoint of 3.0-3.5% target)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1425,7 +1431,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Public Debt Administration, Aug-26 (end-2024 figure cited as 47.7%)</t>
+          <t>Public Debt Administration, Aug-26 (end-2024 figure)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Serbia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Serbia_Sovereign_Model.xlsx
@@ -647,12 +647,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Oct-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>National Bank of Serbia</t>
+          <t>National Bank of Serbia, Executive Board decision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -774,17 +774,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>end-Aug-26</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Public Debt Administration (javnidug.gov.rs)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Aug-26</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Public Debt Administration</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15-Dec-26 (Fourth Review mission)</t>
+          <t>Fourth Review mission 15-Dec-26</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Public Debt Administration, Aug-26 (end-2024 figure)</t>
+          <t>Public Debt Administration, Aug-26 (end-2024 value 47.7%)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Serbia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Serbia_Sovereign_Model.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Statistical Office of the Republic of Serbia</t>
+          <t>Statistical Office of the Republic of Serbia (stat.gov.rs)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Statistical Office of the Republic of Serbia</t>
+          <t>Statistical Office of the Republic of Serbia (stat.gov.rs)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>end-Aug-26</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Serbia (goods and services imports)</t>
+          <t>National Bank of Serbia (nbs.rs), goods and services imports</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Public Debt Administration, Aug-26 (end-2024 value 47.7%)</t>
+          <t>Public Debt Administration (end-2024 figure cited in Aug-26 report), Aug-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Serbia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Serbia_Sovereign_Model.xlsx
@@ -700,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Statistical Office of the Republic of Serbia (stat.gov.rs)</t>
+          <t>Statistical Office of the Republic of Serbia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Statistical Office of the Republic of Serbia (stat.gov.rs)</t>
+          <t>Statistical Office of the Republic of Serbia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Serbia (nbs.rs), goods and services imports</t>
+          <t>National Bank of Serbia (goods and services imports)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fourth Review mission 15-Dec-26</t>
+          <t>15-Dec-26 (Fourth Review mission)</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1335,6 +1335,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1347,7 +1352,8 @@
       </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1359,7 +1365,8 @@
       <c r="C3" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Statistical Office of the Republic of Serbia, Sep-26 (midpoint of 3.2-3.4% projection)</t>
         </is>
@@ -1373,7 +1380,8 @@
       </c>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1385,9 +1393,10 @@
       <c r="C5" s="2" t="n">
         <v>-4.1</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>National Bank of Serbia / IMF, Jun-26</t>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>National Bank of Serbia / IMF, 30-Jun-26</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1410,8 @@
       <c r="C6" s="2" t="n">
         <v>-3.25</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Ministry of Finance, Aug-26 (midpoint of 3.0-3.5% target)</t>
         </is>
@@ -1415,7 +1425,8 @@
       </c>
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1429,9 +1440,12 @@
       <c r="C8" s="2" t="n">
         <v>43.3</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Public Debt Administration (end-2024 figure cited in Aug-26 report), Aug-26</t>
+      <c r="D8" s="2" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Public Debt Administration, 30-Sep-26 (2024 end-year 47.7; latest is end-Aug-26)</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1457,8 @@
       </c>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1453,7 +1468,8 @@
       </c>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1463,7 +1479,8 @@
       </c>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1473,7 +1490,8 @@
       </c>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Serbia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Serbia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/serbia.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/serbia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Serbia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Serbia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/serbia.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/serbia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Serbia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Serbia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/serbia.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/serbia.json</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>35.71</v>
+        <v>33.849</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
